--- a/stories/arbres/ATOM-REL.PAR.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Enzo est au parc avec maman. Le gravier craque sous les pieds. Enzo aime le tricycle rouge. Lila est déjà dessus. Le tricycle avance tout doux. Enzo a envie. Il s'approche. Maman dit : on peut attendre. Attendre, c'est rester près. Enzo pose les pieds au sol. Il compte. Un. Deux. Trois. Lila pédale encore. Enzo attend. Maman tient sa main. Le vent est doux. Lila descend. Maman dit : puis mon tour. Enzo dit : puis mon tour. Enzo s'assoit. Il pédale. Ses genoux bougent. Lila attend maintenant. Parce qu'il a attendu, c'est son tour. Maman dit : on attend. Puis mon tour arrive. Enzo sourit. Le guidon est lisse. Une feuille tombe. Maman reste tout près. Enzo rend le tricycle. Lila reprend. Puis encore un tour. Enzo attend de nouveau. Puis mon tour revient.</t>
+          <t>Enzo est au parc avec maman. Le gravier craque sous les pieds. Enzo aime le tricycle rouge. Lila est déjà dessus. Le tricycle avance tout doux. Enzo a envie. Il s'approche. On peut attendre. Attendre, c'est rester près. Enzo pose les pieds au sol. Il compte. Un. Deux. Trois. Lila pédale encore. Enzo attend. Maman tient sa main. Le vent est doux. Lila descend. Puis mon tour. Puis mon tour. Enzo s'assoit. Il pédale. Ses genoux bougent. Lila attend maintenant. Parce qu'il a attendu, c'est son tour. On attend. Puis mon tour arrive. Enzo sourit. Le guidon est lisse. Une feuille tombe. Maman reste tout près. Enzo rend le tricycle. Lila reprend. Puis encore un tour. Enzo attend de nouveau. Puis mon tour revient.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Enzo est au parc avec maman. Le gravier craque sous les pieds. Enzo aime le tricycle rouge. Lila est déjà dessus. Le tricycle avance tout doux. Enzo a envie. Il s'approche.
+maman|On peut attendre. Attendre, c'est rester près.
+narrateur|Enzo pose les pieds au sol. Il compte. Un. Deux. Trois. Lila pédale encore. Enzo attend. Maman tient sa main. Le vent est doux. Lila descend.
+maman|Puis mon tour.
+enfant-m|Puis mon tour.
+narrateur|Enzo s'assoit. Il pédale. Ses genoux bougent. Lila attend maintenant. Parce qu'il a attendu, c'est son tour.
+maman|On attend.
+narrateur|Puis mon tour arrive. Enzo sourit. Le guidon est lisse. Une feuille tombe. Maman reste tout près. Enzo rend le tricycle. Lila reprend. Puis encore un tour. Enzo attend de nouveau. Puis mon tour revient.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pédale. Que fait Enzo ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Enzo a su attendre. Puis mon tour est venu. Il a pédalé. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Enzo descend. Il prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 narrateur|Puis mon tour arrive. Enzo sourit. Le guidon est lisse. Une feuille tombe. Maman reste tout près. Enzo rend le tricycle. Lila reprend. Puis encore un tour. Enzo attend de nouveau. Puis mon tour revient.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Lila pédale. Que fait Enzo ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,7 @@
           <t>narrateur|Enzo a su attendre. Puis mon tour est venu. Il a pédalé. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1850,7 @@
           <t>narrateur|Enzo descend. Il prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2061,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.PAR.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enzo attend le tricycle</t>
+          <t>Nino attend le tricycle</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>REL.PAR.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la pluie, le chemin brille. Sarah pédale déjà. Nino pose les pieds au sol. Il attend. Puis c'est son tour.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Enzo est au parc avec maman. Le gravier craque sous les pieds. Enzo aime le tricycle rouge. Lila est déjà dessus. Le tricycle avance tout doux. Enzo a envie. Il s'approche. On peut attendre. Attendre, c'est rester près. Enzo pose les pieds au sol. Il compte. Un. Deux. Trois. Lila pédale encore. Enzo attend. Maman tient sa main. Le vent est doux. Lila descend. Puis mon tour. Puis mon tour. Enzo s'assoit. Il pédale. Ses genoux bougent. Lila attend maintenant. Parce qu'il a attendu, c'est son tour. On attend. Puis mon tour arrive. Enzo sourit. Le guidon est lisse. Une feuille tombe. Maman reste tout près. Enzo rend le tricycle. Lila reprend. Puis encore un tour. Enzo attend de nouveau. Puis mon tour revient.</t>
+          <t>Après la pluie, le chemin du parc brille. Une feuille collée reste sur une chaussure. Nino marche avec maman. Leurs pas font un petit bruit mouillé. La maison est juste derrière les tilleuls. Papa range le linge, tout près. Ça sent l'herbe coupée. Un oiseau secoue ses ailes. Tu as vu la feuille, Nino ? Elle est collée, maman. On la pose près du banc ? Nino pose la feuille. Le banc est encore un peu humide. Une flaque ronde brille près du banc. Le parc a encore de l'eau, hein ? Oui, maman. En ce moment, le parc est calme. Le gravier craque sous les pieds. Un tricycle rouge attend sur le chemin. Sarah est déjà dessus. Elle pédale tout doux. Les roues font un petit chant. Nino a envie du tricycle. Maman, je veux pédaler. On peut attendre. Sarah finit son tour. Puis c'est le tien. Nino pose les pieds au sol. Il reste près de maman. Il compte tout bas. Un. Deux. Trois. Sarah pédale encore un peu. Le vent est doux sur les joues. Tu attends bien, Nino. Tes pieds restent au sol. Bravo. Une autre feuille tombe. Tu l'as vue tomber ? Oui, maman. Sarah tourne près du banc. Le guidon est lisse et rouge. Nino attend encore. On reste près. Puis ce sera ton tour. Sarah ralentit. Nino serre la main de maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Enzo est au parc avec maman. Le gravier craque sous les pieds. Enzo aime le tricycle rouge. Lila est déjà dessus. Le tricycle avance tout doux. Enzo a envie. Il s'approche.
-maman|On peut attendre. Attendre, c'est rester près.
-narrateur|Enzo pose les pieds au sol. Il compte. Un. Deux. Trois. Lila pédale encore. Enzo attend. Maman tient sa main. Le vent est doux. Lila descend.
-maman|Puis mon tour.
-enfant-m|Puis mon tour.
-narrateur|Enzo s'assoit. Il pédale. Ses genoux bougent. Lila attend maintenant. Parce qu'il a attendu, c'est son tour.
-maman|On attend.
-narrateur|Puis mon tour arrive. Enzo sourit. Le guidon est lisse. Une feuille tombe. Maman reste tout près. Enzo rend le tricycle. Lila reprend. Puis encore un tour. Enzo attend de nouveau. Puis mon tour revient.</t>
+          <t>narrateur|Après la pluie, le chemin du parc brille.
+narrateur|Une feuille collée reste sur une chaussure.
+narrateur|Nino marche avec maman.
+narrateur|Leurs pas font un petit bruit mouillé.
+narrateur|La maison est juste derrière les tilleuls.
+narrateur|Papa range le linge, tout près.
+narrateur|Ça sent l'herbe coupée.
+narrateur|Un oiseau secoue ses ailes.
+maman|Tu as vu la feuille, Nino ?
+enfant-m|Elle est collée, maman.
+maman|On la pose près du banc ?
+narrateur|Nino pose la feuille.
+narrateur|Le banc est encore un peu humide.
+narrateur|Une flaque ronde brille près du banc.
+maman|Le parc a encore de l'eau, hein ?
+enfant-m|Oui, maman.
+narrateur|En ce moment, le parc est calme.
+narrateur|Le gravier craque sous les pieds.
+narrateur|Un tricycle rouge attend sur le chemin.
+narrateur|Sarah est déjà dessus.
+narrateur|Elle pédale tout doux.
+narrateur|Les roues font un petit chant.
+narrateur|Nino a envie du tricycle.
+enfant-m|Maman, je veux pédaler.
+maman|On peut attendre.
+maman|Sarah finit son tour.
+maman|Puis c'est le tien.
+narrateur|Nino pose les pieds au sol.
+narrateur|Il reste près de maman.
+narrateur|Il compte tout bas.
+enfant-m|Un.
+enfant-m|Deux.
+enfant-m|Trois.
+narrateur|Sarah pédale encore un peu.
+narrateur|Le vent est doux sur les joues.
+maman|Tu attends bien, Nino.
+maman|Tes pieds restent au sol.
+maman|Bravo.
+narrateur|Une autre feuille tombe.
+maman|Tu l'as vue tomber ?
+enfant-m|Oui, maman.
+narrateur|Sarah tourne près du banc.
+narrateur|Le guidon est lisse et rouge.
+narrateur|Nino attend encore.
+maman|On reste près.
+maman|Puis ce sera ton tour.
+narrateur|Sarah ralentit.
+narrateur|Nino serre la main de maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1351,7 +1408,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lila pédale. Que fait Enzo ?</t>
+          <t>Sarah pédale. Que fait Nino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1564,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Lila pédale. Que fait Enzo ?</t>
+          <t>narrateur|Sarah pédale.
+narrateur|Que fait Nino ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Enzo a su attendre. Puis mon tour est venu. Il a pédalé. Maman est là.</t>
+          <t>Sarah descend du tricycle. Maintenant. Puis c'est ton tour. Puis mon tour. Nino s'assoit. Il pédale. Ses genoux bougent tout doux. Le gravier chante sous les roues. Bravo, Nino. Tu as attendu. C'est du bon travail. Le guidon est lisse, maman. Oui. Il est doux sous les mains. Sarah attend maintenant, près du banc. Parce que tu as attendu, c'est ton tour. Nino passe près de la flaque. Tu pédales bien, tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1737,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Enzo a su attendre. Puis mon tour est venu. Il a pédalé. Maman est là.</t>
+          <t>narrateur|Sarah descend du tricycle.
+maman|Maintenant.
+maman|Puis c'est ton tour.
+enfant-m|Puis mon tour.
+narrateur|Nino s'assoit.
+narrateur|Il pédale.
+narrateur|Ses genoux bougent tout doux.
+narrateur|Le gravier chante sous les roues.
+maman|Bravo, Nino.
+maman|Tu as attendu.
+maman|C'est du bon travail.
+enfant-m|Le guidon est lisse, maman.
+maman|Oui.
+maman|Il est doux sous les mains.
+narrateur|Sarah attend maintenant, près du banc.
+maman|Parce que tu as attendu, c'est ton tour.
+narrateur|Nino passe près de la flaque.
+maman|Tu pédales bien, tout doux.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1707,7 +1782,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Enzo descend. Il prend la main de maman.</t>
+          <t>Nino s'arrête près du banc. Tu veux laisser le tricycle à Sarah ? Oui, maman. Bravo. On peut prêter. Sarah reprend le tricycle. Nino attend de nouveau. Puis ton tour reviendra. Puis mon tour. Sarah fait un petit tour. Elle revient. C'est encore à toi, Nino. Nino pédale une dernière fois. Puis il descend. Il prend la main de maman. On rentre ? Oui. Le chemin brille encore. La feuille attend près du banc. Tu as bien attendu, deux fois.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1847,7 +1922,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Enzo descend. Il prend la main de maman.</t>
+          <t>narrateur|Nino s'arrête près du banc.
+maman|Tu veux laisser le tricycle à Sarah ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|On peut prêter.
+narrateur|Sarah reprend le tricycle.
+narrateur|Nino attend de nouveau.
+maman|Puis ton tour reviendra.
+enfant-m|Puis mon tour.
+narrateur|Sarah fait un petit tour.
+narrateur|Elle revient.
+maman|C'est encore à toi, Nino.
+narrateur|Nino pédale une dernière fois.
+narrateur|Puis il descend.
+narrateur|Il prend la main de maman.
+maman|On rentre ?
+enfant-m|Oui.
+narrateur|Le chemin brille encore.
+narrateur|La feuille attend près du banc.
+maman|Tu as bien attendu, deux fois.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1875,7 +1969,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis c'était mon tour. Bravo, Nino. Tu as fait du bon travail. Le tricycle rouge reste au soleil. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2015,7 +2109,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai attendu.
+enfant-m|Puis c'était mon tour.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+narrateur|Le tricycle rouge reste au soleil.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2037,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2174,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-04.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Enzo est au parc avec maman. Le gravier craque sous les pieds. Enzo aime le tricycle rouge. Lila est déjà dessus. Le tricycle avance tout doux. Enzo a envie. Il s'approche. Maman dit : on peut &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Attendre, c'est rester près. Enzo pose les pieds au sol. Il compte. Un. Deux. Trois. Lila pédale encore. Enzo attend. Maman tient sa main. Le vent est doux. Lila descend. Maman dit : puis mon tour. Enzo dit : puis mon tour. Enzo s'assoit. Il pédale. Ses genoux bougent. Lila attend maintenant. Parce qu'il a attendu, c'est son tour. Maman dit : on attend. Puis mon tour arrive. Enzo sourit. Le guidon est lisse. Une feuille tombe. Maman reste tout près. Enzo rend le tricycle. Lila reprend. Puis encore un tour. Enzo attend de nouveau. Puis mon tour revient.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après la pluie, le chemin du parc brille. Une feuille collée reste sur une chaussure. Nino marche avec maman. Leurs pas font un petit bruit mouillé. La maison est juste derrière les tilleuls. Papa range le linge, tout près. Ça sent l'herbe coupée. Un oiseau secoue ses ailes. Tu as vu la feuille, Nino ? Elle est collée, maman. On la pose près du banc ? Nino pose la feuille. Le banc est encore un peu humide. Une flaque ronde brille près du banc. Le parc a encore de l'eau, hein ? Oui, maman. En ce moment, le parc est calme. Le gravier craque sous les pieds. Un tricycle rouge attend sur le chemin. Sarah est déjà dessus. Elle pédale tout doux. Les roues font un petit chant. Nino a envie du tricycle. Maman, je veux pédaler. On peut attendre. Sarah finit son tour. Puis c'est le tien. Nino pose les pieds au sol. Il reste près de maman. Il compte tout bas. Un. Deux. Trois. Sarah pédale encore un peu. Le vent est doux sur les joues. Tu attends bien, Nino. Tes pieds restent au sol. Bravo. Une autre feuille tombe. Tu l'as vue tomber ? Oui, maman. Sarah tourne près du banc. Le guidon est lisse et rouge. Nino attend encore. On reste près. Puis ce sera ton tour. Sarah ralentit. Nino serre la main de maman.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Lila pédale. Que fait Enzo ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah pédale. Que fait Nino ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1568,7 +1568,6 @@
 narrateur|Que fait Nino ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1593,12 +1592,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah descend du tricycle. Maintenant. Puis c'est ton tour. Puis mon tour. Nino s'assoit. Il pédale. Ses genoux bougent tout doux. Le gravier chante sous les roues. Bravo, Nino. Tu as attendu. C'est du bon travail. Le guidon est lisse, maman. Oui. Il est doux sous les mains. Sarah attend maintenant, près du banc. Parce que tu as attendu, c'est ton tour. Nino passe près de la flaque. Tu pédales bien, tout doux.</t>
+          <t>Sarah descend du tricycle. Maintenant. Puis c'est ton tour. Puis mon tour. Nino s'assoit. Il pédale. Ses genoux bougent tout doux. Le gravier chante sous les roues. Bravo, Nino. Tu as attendu. Le guidon est lisse, maman. Oui. Il est doux sous les mains. Sarah attend maintenant, près du banc. Parce que tu as attendu, c'est ton tour. Nino passe près de la flaque. Tu pédales bien, tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Enzo a su &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Puis mon tour est venu. Il a pédalé. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah descend du tricycle. Maintenant. Puis c'est ton tour. Puis mon tour. Nino s'assoit. Il pédale. Ses genoux bougent tout doux. Le gravier chante sous les roues. Bravo, Nino. Tu as attendu. Le guidon est lisse, maman. Oui. Il est doux sous les mains. Sarah attend maintenant, près du banc. Parce que tu as attendu, c'est ton tour. Nino passe près de la flaque. Tu pédales bien, tout doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1747,7 +1746,6 @@
 narrateur|Le gravier chante sous les roues.
 maman|Bravo, Nino.
 maman|Tu as attendu.
-maman|C'est du bon travail.
 enfant-m|Le guidon est lisse, maman.
 maman|Oui.
 maman|Il est doux sous les mains.
@@ -1757,7 +1755,6 @@
 maman|Tu pédales bien, tout doux.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Enzo descend. Il prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino s'arrête près du banc. Tu veux laisser le tricycle à Sarah ? Oui, maman. Bravo. On peut prêter. Sarah reprend le tricycle. Nino attend de nouveau. Puis ton tour reviendra. Puis mon tour. Sarah fait un petit tour. Elle revient. C'est encore à toi, Nino. Nino pédale une dernière fois. Puis il descend. Il prend la main de maman. On rentre ? Oui. Le chemin brille encore. La feuille attend près du banc. Tu as bien attendu, deux fois.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1944,7 +1941,6 @@
 maman|Tu as bien attendu, deux fois.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai attendu. Puis c'était mon tour. Bravo, Nino. Tu as fait du bon travail. Le tricycle rouge reste au soleil. L'histoire est finie.</t>
+          <t>J'ai attendu. Puis c'était mon tour. Bravo, Nino. Le tricycle rouge reste au soleil.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai attendu. Puis c'était mon tour. Bravo, Nino. Le tricycle rouge reste au soleil.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2112,12 +2108,9 @@
           <t>enfant-m|J'ai attendu.
 enfant-m|Puis c'était mon tour.
 maman|Bravo, Nino.
-maman|Tu as fait du bon travail.
-narrateur|Le tricycle rouge reste au soleil.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le tricycle rouge reste au soleil.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2136,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2181,6 +2174,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-04.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-04.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Enzo, maman, Lila</t>
+          <t>Nino, Sarah, maman</t>
         </is>
       </c>
     </row>
